--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119723138</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47211-2023 artfynd.xlsx
+++ b/artfynd/A 47211-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>121284766</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
